--- a/questionnaire_templates/008_programming_languages_proficiency_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/008_programming_languages_proficiency_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1177,34 +1177,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>programming_languages_1_choices</t>
+          <t>programming_languages_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>c#</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>programming_languages_1_choices</t>
+          <t>programming_languages_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1250,46 +1250,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>programming_languages_2_choices</t>
+          <t>programming_languages_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>programming_languages_2_choices</t>
+          <t>programming_languages_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1335,53 +1335,53 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SQL</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>programming_languages_3_choices</t>
+          <t>programming_languages_9_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>programming_languages_3_choices</t>
+          <t>programming_languages_9_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>programming_languages_9_choices</t>
+          <t>programming_languages_10_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>programming_languages_9_choices</t>
+          <t>programming_languages_10_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>programming_languages_10_choices</t>
+          <t>programming_languages_11_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>programming_languages_10_choices</t>
+          <t>programming_languages_11_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>programming_languages_11_choices</t>
+          <t>programming_languages_13_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>programming_languages_11_choices</t>
+          <t>programming_languages_13_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>programming_languages_13_choices</t>
+          <t>programming_languages_14_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>programming_languages_13_choices</t>
+          <t>programming_languages_14_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>programming_languages_14_choices</t>
+          <t>programming_languages_15_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>programming_languages_14_choices</t>
+          <t>programming_languages_15_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>programming_languages_15_choices</t>
+          <t>programming_languages_16_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>programming_languages_15_choices</t>
+          <t>programming_languages_16_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>programming_languages_16_choices</t>
+          <t>programming_languages_22_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>programming_languages_16_choices</t>
+          <t>programming_languages_22_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>programming_languages_22_choices</t>
+          <t>programming_languages_23_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>programming_languages_22_choices</t>
+          <t>programming_languages_23_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>programming_languages_23_choices</t>
+          <t>programming_languages_24_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>programming_languages_23_choices</t>
+          <t>programming_languages_24_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1679,40 +1679,6 @@
         </is>
       </c>
       <c r="C34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>programming_languages_24_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>programming_languages_24_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
